--- a/用卷/xlsx/常规科目/1986.xlsx
+++ b/用卷/xlsx/常规科目/1986.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\常规科目\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69BB39E-42C3-4102-A2D6-EFCD6543B62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0856462E-551B-4E06-A15C-22E7527A5203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,19 +205,19 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>广西外语类</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>辽宁文科类</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>辽宁其他类</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>数学、物理为广东卷,英语为MET,其他科目为全国卷</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>辽宁文史类</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西英语类</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -785,7 +785,7 @@
         <v>1986</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>44</v>
@@ -797,7 +797,7 @@
         <v>1986</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>46</v>
@@ -944,7 +944,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D22" s="17"/>
     </row>
@@ -953,7 +953,7 @@
         <v>1986</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>44</v>
